--- a/excel-files/MANILA/DR. BENIGNO V. ALDANA ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/MANILA/DR. BENIGNO V. ALDANA ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B996939B-A929-7F43-A8A2-FE68CC681F5D}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B47E16BF-792C-4248-9B57-58DAB3C46098}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -317,7 +317,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1829,6 +1829,13 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1852,13 +1859,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -2937,6 +2937,13 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2973,13 +2980,6 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3022,7 +3022,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="61" tableBorderDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
   <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
@@ -3039,7 +3039,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
   <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
@@ -3095,7 +3095,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
   <autoFilter ref="A2:AA140" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
@@ -3468,17 +3468,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H98"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.0859375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.84375" customWidth="1"/>
-    <col min="3" max="5" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.1015625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.19921875" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
     <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="29.25" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="21" customHeight="1">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="25.5" customHeight="1">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3596,7 +3596,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="20.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3618,12 +3618,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="39.75" customHeight="1">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="24" customHeight="1">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="20.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3733,12 +3733,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="49.5" customHeight="1">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="27" customHeight="1">
       <c r="A16" s="1">
         <v>3</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="23.25" customHeight="1">
       <c r="A17" s="1">
         <v>3</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="21" customHeight="1">
       <c r="A18" s="1">
         <v>3</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="20.25">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3880,7 +3880,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="28.5" customHeight="1">
       <c r="A21" s="1">
         <v>4</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="24" customHeight="1">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -3932,7 +3932,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="20.25">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="27" customHeight="1">
       <c r="A24" s="1">
         <v>4</v>
       </c>
@@ -3984,7 +3984,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="33.75" customHeight="1">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="33.75" customHeight="1">
       <c r="A26" s="1">
         <v>4</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="33.75" customHeight="1">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="27.75" customHeight="1">
       <c r="A28" s="1">
         <v>4</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="27.75" customHeight="1">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -4106,7 +4106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="27.75" customHeight="1">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -4116,7 +4116,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1">
       <c r="A31" s="1">
         <v>5</v>
       </c>
@@ -4144,7 +4144,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="27.75" customHeight="1">
       <c r="A32" s="1">
         <v>5</v>
       </c>
@@ -4166,7 +4166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="27.75" customHeight="1">
       <c r="A33" s="1">
         <v>5</v>
       </c>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="27.75" customHeight="1">
       <c r="A34" s="1">
         <v>5</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="39" customHeight="1">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="27.75" customHeight="1">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="27.75" customHeight="1">
       <c r="A37" s="1">
         <v>5</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="27.75" customHeight="1">
       <c r="A38" s="1">
         <v>5</v>
       </c>
@@ -4304,7 +4304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="27.75" customHeight="1">
       <c r="A39" s="1">
         <v>5</v>
       </c>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" ht="27.75" customHeight="1">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -4336,7 +4336,7 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="27.75" customHeight="1">
       <c r="A41" s="1">
         <v>6</v>
       </c>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="27.75" customHeight="1">
       <c r="A42" s="1">
         <v>6</v>
       </c>
@@ -4380,7 +4380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="27.75" customHeight="1">
       <c r="A43" s="1">
         <v>6</v>
       </c>
@@ -4402,7 +4402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="27.75" customHeight="1">
       <c r="A44" s="1">
         <v>6</v>
       </c>
@@ -4424,7 +4424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="36.75" customHeight="1">
       <c r="A45" s="1">
         <v>6</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="27.75" customHeight="1">
       <c r="A46" s="1">
         <v>6</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="27.75" customHeight="1">
       <c r="A47" s="1">
         <v>6</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="27.75" customHeight="1">
       <c r="A48" s="1">
         <v>6</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="27.75" customHeight="1">
       <c r="A49" s="1">
         <v>6</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" ht="27.75" customHeight="1">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
@@ -4544,7 +4544,7 @@
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="27.75" customHeight="1">
       <c r="A51" s="10">
         <v>7</v>
       </c>
@@ -4564,7 +4564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="27.75" customHeight="1">
       <c r="A52" s="10">
         <v>7</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="27.75" customHeight="1">
       <c r="A53" s="10">
         <v>7</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="27.75" customHeight="1">
       <c r="A54" s="10">
         <v>7</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="39" customHeight="1">
       <c r="A55" s="10">
         <v>7</v>
       </c>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="27.75" customHeight="1">
       <c r="A56" s="10">
         <v>7</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="27.75" customHeight="1">
       <c r="A57" s="10">
         <v>7</v>
       </c>
@@ -4684,7 +4684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="27.75" customHeight="1">
       <c r="A58" s="10">
         <v>7</v>
       </c>
@@ -4704,7 +4704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="27.75" customHeight="1">
       <c r="A59" s="10">
         <v>7</v>
       </c>
@@ -4724,7 +4724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" ht="27.75" customHeight="1">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -4734,7 +4734,7 @@
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="27.75" customHeight="1">
       <c r="A61" s="10">
         <v>8</v>
       </c>
@@ -4754,7 +4754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="27.75" customHeight="1">
       <c r="A62" s="10">
         <v>8</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="27.75" customHeight="1">
       <c r="A63" s="10">
         <v>8</v>
       </c>
@@ -4794,7 +4794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="27.75" customHeight="1">
       <c r="A64" s="10">
         <v>8</v>
       </c>
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="27.75" customHeight="1">
       <c r="A65" s="10">
         <v>8</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="27.75" customHeight="1">
       <c r="A66" s="10">
         <v>8</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="27.75" customHeight="1">
       <c r="A67" s="10">
         <v>8</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="27.75" customHeight="1">
       <c r="A68" s="10">
         <v>8</v>
       </c>
@@ -4894,7 +4894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="27.75" customHeight="1">
       <c r="A69" s="10">
         <v>8</v>
       </c>
@@ -4914,7 +4914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" ht="27.75" customHeight="1">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
@@ -4924,7 +4924,7 @@
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="27.75" customHeight="1">
       <c r="A71" s="10">
         <v>9</v>
       </c>
@@ -4944,7 +4944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="27.75" customHeight="1">
       <c r="A72" s="10">
         <v>9</v>
       </c>
@@ -4964,7 +4964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="27.75" customHeight="1">
       <c r="A73" s="10">
         <v>9</v>
       </c>
@@ -4984,7 +4984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="27.75" customHeight="1">
       <c r="A74" s="10">
         <v>9</v>
       </c>
@@ -5004,7 +5004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="27.75" customHeight="1">
       <c r="A75" s="10">
         <v>9</v>
       </c>
@@ -5024,7 +5024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="27.75" customHeight="1">
       <c r="A76" s="10">
         <v>9</v>
       </c>
@@ -5044,7 +5044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="27.75" customHeight="1">
       <c r="A77" s="10">
         <v>9</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" ht="27.75" customHeight="1">
       <c r="A78" s="10">
         <v>9</v>
       </c>
@@ -5084,7 +5084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="27.75" customHeight="1">
       <c r="A79" s="10">
         <v>9</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" ht="27.75" customHeight="1">
       <c r="A80" s="7"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -5114,7 +5114,7 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="27.75" customHeight="1">
       <c r="A81" s="10">
         <v>10</v>
       </c>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="27.75" customHeight="1">
       <c r="A82" s="10">
         <v>10</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="27.75" customHeight="1">
       <c r="A83" s="10">
         <v>10</v>
       </c>
@@ -5174,7 +5174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="27.75" customHeight="1">
       <c r="A84" s="10">
         <v>10</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" ht="27.75" customHeight="1">
       <c r="A85" s="10">
         <v>10</v>
       </c>
@@ -5214,7 +5214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="27.75" customHeight="1">
       <c r="A86" s="10">
         <v>10</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="27.75" customHeight="1">
       <c r="A87" s="10">
         <v>10</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="27.75" customHeight="1">
       <c r="A88" s="10">
         <v>10</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="27.75" customHeight="1">
       <c r="A89" s="10">
         <v>10</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" ht="27.75" customHeight="1">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
@@ -5304,7 +5304,7 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" ht="39.75" customHeight="1">
       <c r="A91" s="1" t="s">
         <v>24</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" ht="27.75" customHeight="1">
       <c r="A92" s="1" t="s">
         <v>24</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" ht="27.75" customHeight="1">
       <c r="A93" s="1" t="s">
         <v>24</v>
       </c>
@@ -5364,7 +5364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="27.75" customHeight="1">
       <c r="A94" s="1" t="s">
         <v>24</v>
       </c>
@@ -5384,7 +5384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="40.5" customHeight="1">
       <c r="A95" s="1" t="s">
         <v>24</v>
       </c>
@@ -5404,7 +5404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="38.25" customHeight="1">
       <c r="A96" s="1" t="s">
         <v>24</v>
       </c>
@@ -5424,7 +5424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" ht="27.75" customHeight="1">
       <c r="A97" s="1" t="s">
         <v>24</v>
       </c>
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" ht="47.25" customHeight="1">
       <c r="A98" s="1" t="s">
         <v>24</v>
       </c>
@@ -5471,8 +5471,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5487,36 +5487,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AA127"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.4140625" customWidth="1"/>
-    <col min="2" max="2" width="27.84375" customWidth="1"/>
-    <col min="3" max="3" width="17.08203125" customWidth="1"/>
-    <col min="4" max="4" width="26.09765625" customWidth="1"/>
-    <col min="5" max="5" width="23.13671875" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5625" customWidth="1"/>
-    <col min="8" max="9" width="20.84765625" customWidth="1"/>
-    <col min="10" max="10" width="13.71875" customWidth="1"/>
-    <col min="11" max="11" width="35.51171875" customWidth="1"/>
-    <col min="12" max="12" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.609375" customWidth="1"/>
-    <col min="14" max="15" width="20.84765625" customWidth="1"/>
-    <col min="16" max="16" width="21.5234375" customWidth="1"/>
-    <col min="17" max="17" width="33.359375" customWidth="1"/>
-    <col min="18" max="18" width="25.828125" customWidth="1"/>
-    <col min="19" max="19" width="32.8203125" customWidth="1"/>
-    <col min="20" max="21" width="20.84765625" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="35.5703125" customWidth="1"/>
+    <col min="12" max="12" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.5703125" customWidth="1"/>
+    <col min="14" max="15" width="20.85546875" customWidth="1"/>
+    <col min="16" max="16" width="21.5703125" customWidth="1"/>
+    <col min="17" max="17" width="33.42578125" customWidth="1"/>
+    <col min="18" max="18" width="25.85546875" customWidth="1"/>
+    <col min="19" max="19" width="32.85546875" customWidth="1"/>
+    <col min="20" max="21" width="20.85546875" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25.01953125" customWidth="1"/>
-    <col min="24" max="24" width="15.33203125" customWidth="1"/>
-    <col min="25" max="25" width="20.84765625" customWidth="1"/>
-    <col min="26" max="26" width="14.796875" customWidth="1"/>
-    <col min="27" max="27" width="15.19921875" customWidth="1"/>
+    <col min="23" max="23" width="25" customWidth="1"/>
+    <col min="24" max="24" width="15.28515625" customWidth="1"/>
+    <col min="25" max="25" width="20.85546875" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="D1" s="42" t="s">
         <v>33</v>
       </c>
@@ -5550,7 +5550,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -5633,7 +5633,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="30.6" customHeight="1">
       <c r="A3" s="39" t="s">
         <v>61</v>
       </c>
@@ -5700,7 +5700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -5712,7 +5712,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="34.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="20.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5850,7 +5850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="20.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5919,7 +5919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="20.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="20.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6057,7 +6057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="20.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6126,7 +6126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="20.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6195,7 +6195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="20.25">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6264,7 +6264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6277,7 +6277,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="34.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6346,7 +6346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="20.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6415,7 +6415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="20.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6484,7 +6484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="20.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="20.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6622,7 +6622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="20.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="20.25">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6760,7 +6760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="20.25">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6829,7 +6829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6843,7 +6843,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="34.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="20.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -6981,7 +6981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="20.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7050,7 +7050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="20.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7119,7 +7119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="20.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7188,7 +7188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="20.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7257,7 +7257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="20.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7326,7 +7326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="20.25">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="20.25">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7478,7 +7478,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="20.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7547,7 +7547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="20.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7616,7 +7616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="20.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7685,7 +7685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="20.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7754,7 +7754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="20.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7823,7 +7823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="20.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="20.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -7961,7 +7961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="20.25">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8030,7 +8030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="20.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8113,7 +8113,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="20.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8182,7 +8182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="20.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8251,7 +8251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="20.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8320,7 +8320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="20.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8389,7 +8389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="20.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8458,7 +8458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="20.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8527,7 +8527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="20.25">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8596,7 +8596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="20.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8665,7 +8665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="20.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8734,7 +8734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8748,7 +8748,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="20.25">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -8817,7 +8817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" ht="20.25">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8886,7 +8886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" ht="20.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="20.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9024,7 +9024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="20.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9093,7 +9093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="20.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9162,7 +9162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="20.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9231,7 +9231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" ht="20.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9300,7 +9300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" ht="20.25">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9383,7 +9383,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="20.25">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9452,7 +9452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" ht="20.25">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9521,7 +9521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="20.25">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9590,7 +9590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" ht="20.25">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9659,7 +9659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" ht="20.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9728,7 +9728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="20.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9797,7 +9797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="20.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9866,7 +9866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="20.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -9935,7 +9935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="20.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -10004,7 +10004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -10018,7 +10018,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="20.25">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10087,7 +10087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="20.25">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10156,7 +10156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="20.25">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10225,7 +10225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" ht="20.25">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="20.25">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10363,7 +10363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" ht="20.25">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10432,7 +10432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" ht="20.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10501,7 +10501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" ht="20.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10570,7 +10570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" ht="20.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10639,7 +10639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10653,7 +10653,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" ht="20.25">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10722,7 +10722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" ht="20.25">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10791,7 +10791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" ht="20.25">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10860,7 +10860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" ht="20.25">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -10929,7 +10929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" ht="20.25">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -10998,7 +10998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" ht="20.25">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11067,7 +11067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" ht="20.25">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11136,7 +11136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" ht="20.25">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11205,7 +11205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" ht="20.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11274,7 +11274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11288,7 +11288,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" ht="20.25">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11357,7 +11357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" ht="20.25">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11426,7 +11426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" ht="20.25">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11495,7 +11495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" ht="20.25">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11564,7 +11564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" ht="20.25">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11633,7 +11633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" ht="20.25">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11702,7 +11702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" ht="20.25">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11771,7 +11771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" ht="20.25">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11840,7 +11840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" ht="20.25">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -11909,7 +11909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -11923,7 +11923,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" ht="34.5">
       <c r="A103" s="1" t="s">
         <v>24</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" ht="20.25">
       <c r="A104" s="1" t="s">
         <v>24</v>
       </c>
@@ -12061,7 +12061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" ht="20.25">
       <c r="A105" s="1" t="s">
         <v>24</v>
       </c>
@@ -12130,7 +12130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" ht="20.25">
       <c r="A106" s="1" t="s">
         <v>24</v>
       </c>
@@ -12199,7 +12199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" ht="34.5">
       <c r="A107" s="1" t="s">
         <v>24</v>
       </c>
@@ -12268,7 +12268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" ht="34.5">
       <c r="A108" s="1" t="s">
         <v>24</v>
       </c>
@@ -12337,7 +12337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" ht="34.5">
       <c r="A109" s="1" t="s">
         <v>24</v>
       </c>
@@ -12406,7 +12406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" ht="34.5">
       <c r="A110" s="1" t="s">
         <v>24</v>
       </c>
@@ -12475,7 +12475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12486,7 +12486,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" ht="20.25">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12548,7 +12548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" ht="20.25">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12610,7 +12610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" ht="20.25">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12672,7 +12672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" ht="20.25">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12734,7 +12734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" ht="20.25">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12796,7 +12796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" ht="20.25">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12858,7 +12858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" ht="20.25">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -12920,7 +12920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" ht="20.25">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -12982,7 +12982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" ht="20.25">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13044,7 +13044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" ht="20.25">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13106,7 +13106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" ht="20.25">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13168,7 +13168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" ht="20.25">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13230,7 +13230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" ht="20.25">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13292,7 +13292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" ht="20.25">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13354,7 +13354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" ht="20.25">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13416,7 +13416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:27" ht="20.25">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13473,186 +13473,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13672,8 +13492,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13691,35 +13511,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AB140"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.4140625" customWidth="1"/>
-    <col min="2" max="2" width="27.84375" customWidth="1"/>
-    <col min="3" max="3" width="17.08203125" customWidth="1"/>
-    <col min="4" max="4" width="16.41015625" customWidth="1"/>
-    <col min="5" max="5" width="23.13671875" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5625" customWidth="1"/>
-    <col min="8" max="9" width="20.84765625" customWidth="1"/>
-    <col min="10" max="10" width="13.71875" customWidth="1"/>
-    <col min="11" max="11" width="24.48046875" customWidth="1"/>
-    <col min="12" max="12" width="18.16015625" customWidth="1"/>
-    <col min="13" max="15" width="20.84765625" customWidth="1"/>
-    <col min="16" max="16" width="21.5234375" customWidth="1"/>
-    <col min="17" max="17" width="29.19140625" customWidth="1"/>
-    <col min="18" max="18" width="25.828125" customWidth="1"/>
-    <col min="19" max="19" width="32.8203125" customWidth="1"/>
-    <col min="20" max="21" width="20.84765625" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="24.42578125" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" customWidth="1"/>
+    <col min="13" max="15" width="20.85546875" customWidth="1"/>
+    <col min="16" max="16" width="21.5703125" customWidth="1"/>
+    <col min="17" max="17" width="29.140625" customWidth="1"/>
+    <col min="18" max="18" width="25.85546875" customWidth="1"/>
+    <col min="19" max="19" width="32.85546875" customWidth="1"/>
+    <col min="20" max="21" width="20.85546875" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25.01953125" customWidth="1"/>
-    <col min="24" max="24" width="15.33203125" customWidth="1"/>
-    <col min="25" max="25" width="20.84765625" customWidth="1"/>
-    <col min="26" max="26" width="14.796875" customWidth="1"/>
-    <col min="27" max="27" width="15.19921875" customWidth="1"/>
+    <col min="23" max="23" width="25" customWidth="1"/>
+    <col min="24" max="24" width="15.28515625" customWidth="1"/>
+    <col min="25" max="25" width="20.85546875" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
       <c r="D1" s="42" t="s">
         <v>33</v>
@@ -13754,7 +13574,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -13837,7 +13657,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="34.5">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -13906,7 +13726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="20.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -13975,7 +13795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="20.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -14044,7 +13864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="20.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14113,7 +13933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="20.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14182,7 +14002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="20.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14251,7 +14071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="20.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14320,7 +14140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="20.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14389,8 +14209,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" s="7" customFormat="1"/>
+    <row r="12" spans="1:27" ht="34.5">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14459,7 +14279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="20.25">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14528,7 +14348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="20.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14597,7 +14417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="20.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14666,7 +14486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="20.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14735,7 +14555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="20.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14804,7 +14624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="20.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -14873,7 +14693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="20.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -14942,8 +14762,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" s="7" customFormat="1"/>
+    <row r="21" spans="1:27" ht="34.5">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -15012,7 +14832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="20.25">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15081,7 +14901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="20.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15150,7 +14970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="20.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15219,7 +15039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="20.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15288,7 +15108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="20.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15357,7 +15177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="20.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15426,7 +15246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="20.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15495,7 +15315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="20.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15564,8 +15384,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" s="7" customFormat="1"/>
+    <row r="31" spans="1:27" ht="20.25">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15634,7 +15454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="20.25">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15703,7 +15523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="20.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15772,7 +15592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="20.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15841,7 +15661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="20.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -15910,7 +15730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="20.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -15979,7 +15799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="20.25">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -16048,7 +15868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="20.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16117,7 +15937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="20.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16186,7 +16006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="20.25">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16255,7 +16075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="20.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16324,8 +16144,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" s="7" customFormat="1"/>
+    <row r="43" spans="1:27" ht="20.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16394,7 +16214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="20.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16463,7 +16283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="20.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16532,7 +16352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="20.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16601,7 +16421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="20.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16670,7 +16490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="20.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16739,7 +16559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="20.25">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -16808,7 +16628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="20.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -16877,7 +16697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="20.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -16946,7 +16766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" ht="20.25">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -17015,7 +16835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="20.25">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -17084,8 +16904,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" s="7" customFormat="1"/>
+    <row r="55" spans="1:27" ht="20.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17154,7 +16974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="20.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17223,7 +17043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="20.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17292,7 +17112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="20.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17361,7 +17181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="20.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17430,7 +17250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" ht="20.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17499,7 +17319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" ht="20.25">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17568,7 +17388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" ht="20.25">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17637,7 +17457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="20.25">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17706,7 +17526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" ht="20.25">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -17775,7 +17595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="20.25">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -17844,8 +17664,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" s="7" customFormat="1"/>
+    <row r="67" spans="1:27" ht="20.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -17914,7 +17734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="20.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -17983,7 +17803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="20.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -18052,7 +17872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="20.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18121,7 +17941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="20.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18190,7 +18010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" ht="20.25">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18259,7 +18079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="20.25">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18328,7 +18148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="20.25">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18397,7 +18217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="20.25">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18466,7 +18286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" ht="20.25">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18535,7 +18355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="20.25">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18604,8 +18424,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" s="7" customFormat="1"/>
+    <row r="79" spans="1:27" ht="20.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18674,7 +18494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" ht="20.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18743,7 +18563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" ht="20.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -18812,7 +18632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" ht="20.25">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18881,7 +18701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" ht="20.25">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -18950,7 +18770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" ht="20.25">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -19019,7 +18839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" ht="20.25">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -19088,7 +18908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" ht="20.25">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19157,7 +18977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" ht="20.25">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19226,7 +19046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" ht="20.25">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19295,7 +19115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" ht="20.25">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19364,8 +19184,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" s="7" customFormat="1"/>
+    <row r="91" spans="1:27" ht="20.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19434,7 +19254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" ht="20.25">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19503,7 +19323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" ht="20.25">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19572,7 +19392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" ht="20.25">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19641,7 +19461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" ht="20.25">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19710,7 +19530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" ht="20.25">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -19779,7 +19599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" ht="20.25">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -19848,7 +19668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" ht="20.25">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -19917,7 +19737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" ht="20.25">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -19986,7 +19806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" ht="20.25">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -20055,7 +19875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" ht="20.25">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20124,8 +19944,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="103" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" s="7" customFormat="1"/>
+    <row r="103" spans="1:27" ht="20.25">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20194,7 +20014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" ht="20.25">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20263,7 +20083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" ht="20.25">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20332,7 +20152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" ht="20.25">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20401,7 +20221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" ht="20.25">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20470,7 +20290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" ht="20.25">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20539,7 +20359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" ht="20.25">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20608,7 +20428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" ht="20.25">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -20677,7 +20497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" ht="20.25">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20746,7 +20566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" ht="20.25">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -20815,7 +20635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:28" ht="20.25">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -20884,8 +20704,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="115" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:28" s="7" customFormat="1"/>
+    <row r="115" spans="1:28" ht="34.5">
       <c r="A115" s="1" t="s">
         <v>24</v>
       </c>
@@ -20954,7 +20774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:28" ht="20.25">
       <c r="A116" s="1" t="s">
         <v>24</v>
       </c>
@@ -21023,7 +20843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:28" ht="20.25">
       <c r="A117" s="1" t="s">
         <v>24</v>
       </c>
@@ -21092,7 +20912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:28" ht="20.25">
       <c r="A118" s="1" t="s">
         <v>24</v>
       </c>
@@ -21161,7 +20981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:28" ht="34.5">
       <c r="A119" s="1" t="s">
         <v>24</v>
       </c>
@@ -21230,7 +21050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:28" ht="34.5">
       <c r="A120" s="1" t="s">
         <v>24</v>
       </c>
@@ -21299,7 +21119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:28" ht="34.5">
       <c r="A121" s="1" t="s">
         <v>24</v>
       </c>
@@ -21368,7 +21188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:28" ht="34.5">
       <c r="A122" s="1" t="s">
         <v>24</v>
       </c>
@@ -21437,8 +21257,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:28" s="7" customFormat="1"/>
+    <row r="124" spans="1:28">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -21468,7 +21288,7 @@
       <c r="AA124" s="7"/>
       <c r="AB124" s="7"/>
     </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:28">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -21498,7 +21318,7 @@
       <c r="AA125" s="7"/>
       <c r="AB125" s="7"/>
     </row>
-    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:28">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -21528,7 +21348,7 @@
       <c r="AA126" s="7"/>
       <c r="AB126" s="7"/>
     </row>
-    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:28">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -21558,7 +21378,7 @@
       <c r="AA127" s="7"/>
       <c r="AB127" s="7"/>
     </row>
-    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:28">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -21588,7 +21408,7 @@
       <c r="AA128" s="7"/>
       <c r="AB128" s="7"/>
     </row>
-    <row r="129" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:28">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -21618,7 +21438,7 @@
       <c r="AA129" s="7"/>
       <c r="AB129" s="7"/>
     </row>
-    <row r="130" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:28">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -21648,7 +21468,7 @@
       <c r="AA130" s="7"/>
       <c r="AB130" s="7"/>
     </row>
-    <row r="131" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:28">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -21678,7 +21498,7 @@
       <c r="AA131" s="7"/>
       <c r="AB131" s="7"/>
     </row>
-    <row r="132" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:28">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -21708,7 +21528,7 @@
       <c r="AA132" s="7"/>
       <c r="AB132" s="7"/>
     </row>
-    <row r="133" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:28">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -21738,7 +21558,7 @@
       <c r="AA133" s="7"/>
       <c r="AB133" s="7"/>
     </row>
-    <row r="134" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:28">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -21768,7 +21588,7 @@
       <c r="AA134" s="7"/>
       <c r="AB134" s="7"/>
     </row>
-    <row r="135" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:28">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -21798,7 +21618,7 @@
       <c r="AA135" s="7"/>
       <c r="AB135" s="7"/>
     </row>
-    <row r="136" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:28">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -21828,7 +21648,7 @@
       <c r="AA136" s="7"/>
       <c r="AB136" s="7"/>
     </row>
-    <row r="137" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:28">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -21858,7 +21678,7 @@
       <c r="AA137" s="7"/>
       <c r="AB137" s="7"/>
     </row>
-    <row r="138" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:28">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -21888,7 +21708,7 @@
       <c r="AA138" s="7"/>
       <c r="AB138" s="7"/>
     </row>
-    <row r="139" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:28">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -21918,7 +21738,7 @@
       <c r="AA139" s="7"/>
       <c r="AB139" s="7"/>
     </row>
-    <row r="140" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:28">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
@@ -21948,186 +21768,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22145,8 +21785,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
